--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4bd18a0ebc4b412f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R11b4a0cf841b4908"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R11b4a0cf841b4908"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfffc5178a75b441b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfffc5178a75b441b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb972146c5cd84357"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb972146c5cd84357"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2553ee6e761d4bed"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2553ee6e761d4bed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8d4d2cfbc37f4f19"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8d4d2cfbc37f4f19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0482279c08f649b4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0482279c08f649b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rab6ca9d6bb9042a8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rab6ca9d6bb9042a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R138354021b8e4672"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R138354021b8e4672"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re2b49ee83c50427d"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re2b49ee83c50427d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8ee5af315a244977"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8ee5af315a244977"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R430965e453374f34"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R430965e453374f34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R105d0b6141344c0c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R105d0b6141344c0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcf23cc0aaa52451d"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcf23cc0aaa52451d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb9708757450f4560"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/PageSetupFitToOnePageWide/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb9708757450f4560"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R64dddc4be70f4894"/>
   </x:sheets>
 </x:workbook>
 </file>
